--- a/ADEMINCOL-Central/backend/app/templates_xlsx/SCANC_LINEAS.xlsx
+++ b/ADEMINCOL-Central/backend/app/templates_xlsx/SCANC_LINEAS.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet name="FORMAT" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FORMATO" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="espeso_max_en_inspec">#REF!</definedName>
